--- a/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
+++ b/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6025271-0C93-478B-AF48-E46258C3ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91894F82-F20D-4DEF-BAB6-9BC5BC8BA015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
   <si>
     <t>type</t>
   </si>
@@ -191,12 +191,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>${p_state}</t>
-  </si>
-  <si>
-    <t>${p_location}</t>
   </si>
   <si>
     <t>demo_mda_9999_4_case_mngnt</t>
@@ -856,9 +850,7 @@
       <c r="P3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
@@ -892,9 +884,7 @@
         <v>38</v>
       </c>
       <c r="Q4" s="9"/>
-      <c r="R4" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
@@ -928,9 +918,7 @@
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
     </row>
@@ -939,10 +927,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
@@ -970,10 +958,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9"/>
@@ -1001,10 +989,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="9"/>
@@ -1032,10 +1020,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="9"/>
@@ -1063,10 +1051,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
@@ -1094,10 +1082,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="9"/>
@@ -1125,10 +1113,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="9"/>
@@ -1156,10 +1144,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="9"/>
@@ -1187,10 +1175,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
@@ -1218,10 +1206,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
@@ -1414,10 +1402,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
+++ b/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91894F82-F20D-4DEF-BAB6-9BC5BC8BA015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8BC396-06FF-47D0-9BE0-D835D2896750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,16 +708,16 @@
     <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="5" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
     <col min="6" max="6" width="12" style="5" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="9.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="26.25" style="5" customWidth="1"/>
     <col min="12" max="12" width="9.125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="20.5" style="5" customWidth="1"/>
+    <col min="13" max="13" width="14.625" style="5" customWidth="1"/>
     <col min="14" max="15" width="11" style="5"/>
     <col min="16" max="16" width="11.75" style="5" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="22.125" style="5" bestFit="1" customWidth="1"/>

--- a/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
+++ b/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8BC396-06FF-47D0-9BE0-D835D2896750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1753BAC-8B41-48BF-B104-68E2CDCD2981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="128">
   <si>
     <t>type</t>
   </si>
@@ -154,9 +154,6 @@
     <t>col_3</t>
   </si>
   <si>
-    <t>col_4</t>
-  </si>
-  <si>
     <t>required_message::English</t>
   </si>
   <si>
@@ -166,24 +163,12 @@
     <t>Select District / LGA / County</t>
   </si>
   <si>
-    <t>Enter the village / location / site</t>
-  </si>
-  <si>
-    <t>Enter the ID of village / location / site</t>
-  </si>
-  <si>
     <t>p_state</t>
   </si>
   <si>
     <t>p_district</t>
   </si>
   <si>
-    <t>p_location</t>
-  </si>
-  <si>
-    <t>p_location_id</t>
-  </si>
-  <si>
     <t>p_add_note</t>
   </si>
   <si>
@@ -196,9 +181,6 @@
     <t>demo_mda_9999_4_case_mngnt</t>
   </si>
   <si>
-    <t>(Demo) 4. MDA Case Management Form</t>
-  </si>
-  <si>
     <t>Total Praziquantel distributed</t>
   </si>
   <si>
@@ -229,9 +211,6 @@
     <t>p_total_alb_dist</t>
   </si>
   <si>
-    <t>p_total_mbz_dist</t>
-  </si>
-  <si>
     <t>p_total_ivm_dist</t>
   </si>
   <si>
@@ -257,6 +236,199 @@
   </si>
   <si>
     <t>p_serious_side_effect</t>
+  </si>
+  <si>
+    <t>(Demo) 4. MDA Medicine Use and Case Management Form</t>
+  </si>
+  <si>
+    <t>p_health_facility</t>
+  </si>
+  <si>
+    <t>Enter the Health facility / Sub district</t>
+  </si>
+  <si>
+    <t>${p_district}</t>
+  </si>
+  <si>
+    <t>${p_state}</t>
+  </si>
+  <si>
+    <t>select_multiple disease</t>
+  </si>
+  <si>
+    <t>p_disease</t>
+  </si>
+  <si>
+    <t>Disease covered by the TDM</t>
+  </si>
+  <si>
+    <t>select_multiple medicine</t>
+  </si>
+  <si>
+    <t>p_medicine</t>
+  </si>
+  <si>
+    <t>Select the meicine package</t>
+  </si>
+  <si>
+    <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO'))) and
+not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF'))) and
+not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
+not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
+not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
+not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))and
+not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
+  </si>
+  <si>
+    <t>You cannot select a single medicine together with its combination version</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>ONCHO</t>
+  </si>
+  <si>
+    <t>SCHISTO</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>TRACHOMA</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>IVM</t>
+  </si>
+  <si>
+    <t>IVM+ALB</t>
+  </si>
+  <si>
+    <t>IVM+ALB+DEC</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>TETRA</t>
+  </si>
+  <si>
+    <t>AZM.TAB</t>
+  </si>
+  <si>
+    <t>AZM TAB</t>
+  </si>
+  <si>
+    <t>AZM.SUSP</t>
+  </si>
+  <si>
+    <t>AZM SUSP</t>
+  </si>
+  <si>
+    <t>MEB</t>
+  </si>
+  <si>
+    <t>PZQ</t>
+  </si>
+  <si>
+    <t>PZQ+ALB</t>
+  </si>
+  <si>
+    <t>PZQ+MEB</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
+  </si>
+  <si>
+    <t>p_total_meb_dist</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.TAB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'TETRA')</t>
+  </si>
+  <si>
+    <t>Number of Guinea Worm rumors</t>
+  </si>
+  <si>
+    <t>Number of suspected cases of Leishmaniasis</t>
+  </si>
+  <si>
+    <t>Number of suspected cases of Buruli ulcer</t>
+  </si>
+  <si>
+    <t>p_guinea_worm_rumor</t>
+  </si>
+  <si>
+    <t>p_leish_suspect</t>
+  </si>
+  <si>
+    <t>p_buruli_ulcer_suspect</t>
   </si>
 </sst>
 </file>
@@ -376,15 +548,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -415,13 +584,28 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -702,620 +886,789 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="24.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12" style="5" customWidth="1"/>
-    <col min="7" max="7" width="29.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="26.25" style="5" customWidth="1"/>
-    <col min="12" max="12" width="9.125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="14.625" style="5" customWidth="1"/>
-    <col min="14" max="15" width="11" style="5"/>
-    <col min="16" max="16" width="11.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="22.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11" style="5"/>
+    <col min="1" max="1" width="19.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="42.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="40.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="29.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="26.25" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9.125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.625" style="4" customWidth="1"/>
+    <col min="14" max="15" width="11" style="4"/>
+    <col min="16" max="16" width="11.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="22.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="31.5">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" s="3" customFormat="1">
+      <c r="A2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" s="4" customFormat="1">
-      <c r="A2" s="14" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+    </row>
+    <row r="6" spans="1:21" ht="393.75">
+      <c r="A6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="9" t="s">
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" s="9" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -1326,54 +1679,385 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="23.75" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="11" style="5"/>
+    <col min="1" max="1" width="14.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="23.75" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="13">
+        <v>99</v>
+      </c>
+      <c r="C14" s="22">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="22"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
+    <row r="18" spans="1:3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:C30">
-    <sortCondition ref="B5:B30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C44">
+    <sortCondition ref="B19:B44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1401,11 +2085,11 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>52</v>
+      <c r="A2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
+++ b/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1753BAC-8B41-48BF-B104-68E2CDCD2981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105F52B8-721F-4A8A-9593-ABCA03B18C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={29E5FA98-A6D7-410E-8BA0-91E19670D5A3}</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{29E5FA98-A6D7-410E-8BA0-91E19670D5A3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    medicine</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="140">
   <si>
     <t>type</t>
   </si>
@@ -178,9 +196,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>demo_mda_9999_4_case_mngnt</t>
-  </si>
-  <si>
     <t>Total Praziquantel distributed</t>
   </si>
   <si>
@@ -238,9 +253,6 @@
     <t>p_serious_side_effect</t>
   </si>
   <si>
-    <t>(Demo) 4. MDA Medicine Use and Case Management Form</t>
-  </si>
-  <si>
     <t>p_health_facility</t>
   </si>
   <si>
@@ -268,167 +280,244 @@
     <t>p_medicine</t>
   </si>
   <si>
-    <t>Select the meicine package</t>
-  </si>
-  <si>
-    <t>not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO'))) and
-not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO'))) and
-not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF'))) and
-not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO'))) and
-not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH'))) and
-not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA'))) and
-not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))and
+    <t>You cannot select a single medicine together with its combination version</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>ONCHO</t>
+  </si>
+  <si>
+    <t>SCHISTO</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>TRACHOMA</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>IVM</t>
+  </si>
+  <si>
+    <t>IVM+ALB</t>
+  </si>
+  <si>
+    <t>IVM+ALB+DEC</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>TETRA</t>
+  </si>
+  <si>
+    <t>AZM.TAB</t>
+  </si>
+  <si>
+    <t>AZM TAB</t>
+  </si>
+  <si>
+    <t>AZM.SUSP</t>
+  </si>
+  <si>
+    <t>AZM SUSP</t>
+  </si>
+  <si>
+    <t>MEB</t>
+  </si>
+  <si>
+    <t>PZQ</t>
+  </si>
+  <si>
+    <t>PZQ+ALB</t>
+  </si>
+  <si>
+    <t>PZQ+MEB</t>
+  </si>
+  <si>
+    <t>recorder_id</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
+  </si>
+  <si>
+    <t>p_total_meb_dist</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'AZM.TAB')</t>
+  </si>
+  <si>
+    <t>selected(${p_medicine}, 'TETRA')</t>
+  </si>
+  <si>
+    <t>Number of Guinea Worm rumors</t>
+  </si>
+  <si>
+    <t>Number of suspected cases of Leishmaniasis</t>
+  </si>
+  <si>
+    <t>Number of suspected cases of Buruli ulcer</t>
+  </si>
+  <si>
+    <t>p_guinea_worm_rumor</t>
+  </si>
+  <si>
+    <t>p_leish_suspect</t>
+  </si>
+  <si>
+    <t>p_buruli_ulcer_suspect</t>
+  </si>
+  <si>
+    <t>disease_filter</t>
+  </si>
+  <si>
+    <t>selected(${p_disease}, disease_filter)</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>Cases of other NTDs identified</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>Number of cases with LF lymphoedema</t>
+  </si>
+  <si>
+    <t>Number of cases with LF Hydrocele</t>
+  </si>
+  <si>
+    <t>P_hydrocele_LF</t>
+  </si>
+  <si>
+    <t>not(
+  selected(${p_disease}, 'LF') and
+  selected(${p_disease}, 'ONCHO') and
+  selected(${p_medicine}, 'IVM')
+)
+and
+not(
+  selected(${p_disease}, 'STH') and
+  selected(${p_disease}, 'SCHISTO') and
+  (
+    selected(${p_medicine}, 'ALB') or
+    selected(${p_medicine}, 'MEB') or
+    selected(${p_medicine}, 'PZQ')
+  )
+)
+and
+not(
+  selected(${p_disease}, 'SCHISTO') and
+  not(selected(${p_disease}, 'STH')) and
+  (
+    selected(${p_medicine}, 'PZQ+ALB') or
+    selected(${p_medicine}, 'PZQ+MEB')
+  )
+)
+and
+not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO') and not(selected(${p_disease}, 'LF'))))
+and
+not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO')))
+and
+not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF')))
+and
+not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO')))
+and
+not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
+and
+not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA')))
+and
+not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))
+and
 not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
   </si>
   <si>
-    <t>You cannot select a single medicine together with its combination version</t>
-  </si>
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>LF</t>
-  </si>
-  <si>
-    <t>ONCHO</t>
-  </si>
-  <si>
-    <t>SCHISTO</t>
-  </si>
-  <si>
-    <t>STH</t>
-  </si>
-  <si>
-    <t>TRACHOMA</t>
-  </si>
-  <si>
-    <t>medicine</t>
-  </si>
-  <si>
-    <t>IVM</t>
-  </si>
-  <si>
-    <t>IVM+ALB</t>
-  </si>
-  <si>
-    <t>IVM+ALB+DEC</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>TETRA</t>
-  </si>
-  <si>
-    <t>AZM.TAB</t>
-  </si>
-  <si>
-    <t>AZM TAB</t>
-  </si>
-  <si>
-    <t>AZM.SUSP</t>
-  </si>
-  <si>
-    <t>AZM SUSP</t>
-  </si>
-  <si>
-    <t>MEB</t>
-  </si>
-  <si>
-    <t>PZQ</t>
-  </si>
-  <si>
-    <t>PZQ+ALB</t>
-  </si>
-  <si>
-    <t>PZQ+MEB</t>
-  </si>
-  <si>
-    <t>recorder_id</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'PZQ') or selected(${p_medicine}, 'PZQ+ALB') or selected(${p_medicine}, 'PZQ+MEB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'ALB') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC') or selected(${p_medicine}, 'PZQ+ALB')</t>
-  </si>
-  <si>
-    <t>p_total_meb_dist</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'MEB') or selected(${p_medicine}, 'PZQ+MEB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'IVM') or selected(${p_medicine}, 'IVM+ALB') or selected(${p_medicine}, 'IVM+ALB+DEC')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'IVM+ALB+DEC')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'AZM.SUSP')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'AZM.TAB')</t>
-  </si>
-  <si>
-    <t>selected(${p_medicine}, 'TETRA')</t>
-  </si>
-  <si>
-    <t>Number of Guinea Worm rumors</t>
-  </si>
-  <si>
-    <t>Number of suspected cases of Leishmaniasis</t>
-  </si>
-  <si>
-    <t>Number of suspected cases of Buruli ulcer</t>
-  </si>
-  <si>
-    <t>p_guinea_worm_rumor</t>
-  </si>
-  <si>
-    <t>p_leish_suspect</t>
-  </si>
-  <si>
-    <t>p_buruli_ulcer_suspect</t>
+    <t>p_Lymphoedema_LF</t>
+  </si>
+  <si>
+    <t>Select the medcine package</t>
+  </si>
+  <si>
+    <t>Medicines Distributed</t>
+  </si>
+  <si>
+    <t>(Demo) 4. MDA Medicine Use and Case Management Form V3</t>
+  </si>
+  <si>
+    <t>demo_mda_9999_4_case_mngnt_v3</t>
+  </si>
+  <si>
+    <t>med_distr</t>
+  </si>
+  <si>
+    <t>other_ntd_rep</t>
   </si>
 </sst>
 </file>
@@ -500,11 +589,11 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,6 +603,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +643,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -593,9 +688,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -607,6 +699,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -626,6 +725,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Tinkitina Benjamin" id="{EAF22BBA-3777-455F-8246-41FAFCC22AA3}" userId="c23755edcbb30cff" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -884,19 +989,27 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C6" dT="2026-04-01T12:55:38.23" personId="{EAF22BBA-3777-455F-8246-41FAFCC22AA3}" id="{29E5FA98-A6D7-410E-8BA0-91E19670D5A3}">
+    <text>medicine</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="27.375" style="4" customWidth="1"/>
     <col min="2" max="2" width="28.25" style="4" customWidth="1"/>
     <col min="3" max="3" width="42.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="4" customWidth="1"/>
     <col min="6" max="6" width="40.75" style="4" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.75" style="4" customWidth="1"/>
+    <col min="8" max="8" width="127.625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.375" style="4" customWidth="1"/>
     <col min="10" max="10" width="9.75" style="4" customWidth="1"/>
     <col min="11" max="11" width="26.25" style="4" customWidth="1"/>
@@ -1035,7 +1148,7 @@
         <v>37</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
@@ -1047,10 +1160,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="8"/>
@@ -1071,7 +1184,7 @@
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
@@ -1079,13 +1192,13 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8"/>
@@ -1108,23 +1221,23 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" spans="1:21" ht="393.75">
+    <row r="6" spans="1:21" ht="47.25">
       <c r="A6" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>79</v>
+      <c r="F6" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>75</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -1133,7 +1246,9 @@
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="M6" s="22" t="s">
+        <v>125</v>
+      </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="17"/>
@@ -1144,54 +1259,50 @@
       <c r="U6" s="8"/>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
+      <c r="A7" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
       <c r="H8" s="8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="7" t="s">
@@ -1214,17 +1325,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
       <c r="H9" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="7" t="s">
@@ -1247,17 +1358,17 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
       <c r="H10" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="7" t="s">
@@ -1280,17 +1391,17 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="7" t="s">
@@ -1313,17 +1424,17 @@
         <v>13</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="9"/>
       <c r="H12" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="7" t="s">
@@ -1346,17 +1457,17 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="7" t="s">
@@ -1379,17 +1490,17 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="7" t="s">
@@ -1412,16 +1523,18 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="I15" s="8"/>
       <c r="J15" s="7" t="s">
         <v>14</v>
@@ -1443,10 +1556,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
@@ -1474,10 +1587,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
@@ -1502,23 +1615,17 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>123</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
@@ -1532,47 +1639,53 @@
       <c r="U18" s="8"/>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>118</v>
+      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
@@ -1587,13 +1700,13 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
@@ -1602,7 +1715,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="7" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -1618,19 +1731,23 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="9"/>
+        <v>123</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="J22" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
@@ -1645,19 +1762,23 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="9"/>
+        <v>133</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="J23" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -1670,16 +1791,158 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
     </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.625" style="4" bestFit="1" customWidth="1"/>
@@ -1688,7 +1951,7 @@
     <col min="4" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -1698,156 +1961,159 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C5" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="20" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="20" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="20" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="20" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="20" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="20" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B14" s="13">
         <v>99</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
-      <c r="C15" s="22"/>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="C15" s="21"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
@@ -1858,7 +2124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
@@ -1869,190 +2135,223 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="A19" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="C22" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:4">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:4">
       <c r="A25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C29" s="9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="D29" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="C30" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="D30" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="D31" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C32" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="8" t="s">
+      <c r="C33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="C35" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2086,10 +2385,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>

--- a/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
+++ b/Demo/MDA/demo_mda_9999_4_case_mngnt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105F52B8-721F-4A8A-9593-ABCA03B18C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413E5158-3F94-4B52-A305-BB50264D633F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,6 @@
   </si>
   <si>
     <t>disease_filter</t>
-  </si>
-  <si>
-    <t>selected(${p_disease}, disease_filter)</t>
   </si>
   <si>
     <t>begin group</t>
@@ -518,6 +515,9 @@
   </si>
   <si>
     <t>other_ntd_rep</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selected(${p_disease}, disease_filter)</t>
   </si>
 </sst>
 </file>
@@ -1229,12 +1229,12 @@
         <v>74</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6" s="18" t="s">
         <v>75</v>
@@ -1247,7 +1247,7 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="22" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
@@ -1640,13 +1640,13 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>126</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -1765,10 +1765,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
@@ -1796,10 +1796,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
@@ -1961,7 +1961,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2359,6 +2359,7 @@
     <sortCondition ref="B19:B44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2385,10 +2386,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
